--- a/academias/Física - Estadisticos 20232.xlsx
+++ b/academias/Física - Estadisticos 20232.xlsx
@@ -1384,25 +1384,25 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1416,25 +1416,25 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1451,25 +1451,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1486,25 +1486,25 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>20.8</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1521,25 +1521,25 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1556,25 +1556,25 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>80.8</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>19.2</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1591,25 +1591,25 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1623,25 +1623,25 @@
         <v>123</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>18.7</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1658,25 +1658,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1693,25 +1693,25 @@
         <v>42</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1728,25 +1728,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1763,25 +1763,25 @@
         <v>45</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>13.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1798,25 +1798,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1833,25 +1833,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1865,25 +1865,25 @@
         <v>220</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="F16">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1900,25 +1900,25 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J17">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1935,25 +1935,25 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1970,25 +1970,25 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2005,25 +2005,25 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2037,25 +2037,25 @@
         <v>98</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="F21">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2072,25 +2072,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2104,25 +2104,25 @@
         <v>31</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2133,25 +2133,25 @@
         <v>486</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="F24">
-        <v>486</v>
+        <v>55</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>88.7</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>11.3</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>486</v>
+        <v>1</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -2219,19 +2219,19 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>35.7</v>
+        <v>21.4</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2251,19 +2251,19 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>64.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>35.7</v>
+        <v>21.4</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         <v>16.7</v>
       </c>
       <c r="I4" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>91.7</v>
+        <v>79.2</v>
       </c>
       <c r="H5" s="1">
-        <v>8.300000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="I5" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2356,19 +2356,19 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="H6" s="1">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2391,19 +2391,19 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>84.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H7" s="1">
-        <v>15.4</v>
+        <v>19.2</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2426,19 +2426,19 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>86.7</v>
+        <v>73.3</v>
       </c>
       <c r="H8" s="1">
-        <v>13.3</v>
+        <v>26.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2458,19 +2458,19 @@
         <v>123</v>
       </c>
       <c r="E9">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1">
-        <v>87</v>
+        <v>81.3</v>
       </c>
       <c r="H9" s="1">
-        <v>13</v>
+        <v>18.7</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2493,19 +2493,19 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>2.4</v>
       </c>
       <c r="I11" s="2">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2563,19 +2563,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2598,19 +2598,19 @@
         <v>45</v>
       </c>
       <c r="E13">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>95.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="H13" s="1">
-        <v>4.4</v>
+        <v>13.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2633,19 +2633,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2668,19 +2668,19 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="H15" s="1">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2700,19 +2700,19 @@
         <v>220</v>
       </c>
       <c r="E16">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>95</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2735,19 +2735,19 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H17" s="1">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="I17" s="2">
-        <v>6.4</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2770,19 +2770,19 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H18" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2805,16 +2805,16 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H19" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2">
         <v>9</v>
@@ -2840,19 +2840,19 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I20" s="2">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2872,19 +2872,19 @@
         <v>98</v>
       </c>
       <c r="E21">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>90.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>9.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2907,19 +2907,19 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>41.9</v>
+        <v>71</v>
       </c>
       <c r="H22" s="1">
-        <v>58.1</v>
+        <v>29</v>
       </c>
       <c r="I22" s="2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2939,19 +2939,19 @@
         <v>31</v>
       </c>
       <c r="E23">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1">
-        <v>41.9</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1">
-        <v>58.1</v>
+        <v>29</v>
       </c>
       <c r="I23" s="2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>486</v>
       </c>
       <c r="E24">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F24">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G24" s="1">
-        <v>87.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>12.1</v>
+        <v>11.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J24">
         <v>0</v>

--- a/academias/Física - Estadisticos 20232.xlsx
+++ b/academias/Física - Estadisticos 20232.xlsx
@@ -546,22 +546,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="H2" s="1">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -578,22 +578,22 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="H3" s="1">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E24">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F24">
         <v>59</v>
@@ -1381,28 +1381,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1413,28 +1413,28 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="H3" s="1">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>5.9</v>
       </c>
       <c r="I16" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2130,28 +2130,28 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E24">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F24">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G24" s="1">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="I24" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2216,22 +2216,22 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>78.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2248,22 +2248,22 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>78.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="H3" s="1">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2286,19 +2286,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="H4" s="1">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2321,19 +2321,19 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>79.2</v>
+        <v>95.8</v>
       </c>
       <c r="H5" s="1">
-        <v>20.8</v>
+        <v>4.2</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2356,19 +2356,19 @@
         <v>28</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2391,19 +2391,19 @@
         <v>26</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2426,19 +2426,19 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>73.3</v>
+        <v>93.3</v>
       </c>
       <c r="H8" s="1">
-        <v>26.7</v>
+        <v>6.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2458,19 +2458,19 @@
         <v>123</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F9">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>81.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>18.7</v>
+        <v>4.9</v>
       </c>
       <c r="I9" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2598,19 +2598,19 @@
         <v>45</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2633,19 +2633,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>87.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="H14" s="1">
-        <v>12.9</v>
+        <v>3.2</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>5.3</v>
       </c>
       <c r="I15" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2700,19 +2700,19 @@
         <v>220</v>
       </c>
       <c r="E16">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>94.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H16" s="1">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="I16" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>4.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2770,19 +2770,19 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H18" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I18" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2840,19 +2840,19 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="H20" s="1">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2872,19 +2872,19 @@
         <v>98</v>
       </c>
       <c r="E21">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>93.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="I21" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2907,16 +2907,16 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="H22" s="1">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="I22" s="2">
         <v>6.8</v>
@@ -2939,16 +2939,16 @@
         <v>31</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="H23" s="1">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="I23" s="2">
         <v>6.8</v>
@@ -2965,22 +2965,22 @@
         <v>19</v>
       </c>
       <c r="D24">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E24">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="F24">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1">
-        <v>88.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H24" s="1">
-        <v>11.1</v>
+        <v>5.1</v>
       </c>
       <c r="I24" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
